--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260827.xlsx
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
